--- a/Seleccionados Nacala Porto.xlsx
+++ b/Seleccionados Nacala Porto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/NEXUS/2026/Dash_Nexus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{E585F9BD-210C-497E-8CEC-392C8BD29361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1CCC94C-0872-4269-A575-EFE22ECF8F04}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{E585F9BD-210C-497E-8CEC-392C8BD29361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F610FB7-648E-4F6D-BA29-50DB3A5A26F2}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{192259D9-C009-46C1-BCB0-30DA2EA98EC4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{192259D9-C009-46C1-BCB0-30DA2EA98EC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Seleccionados Nacala Porto" sheetId="1" r:id="rId1"/>
@@ -7007,10 +7007,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -64936,6 +64932,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
@@ -65170,17 +65177,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -65191,6 +65187,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3DA60A8-A10C-4376-830A-0871C6C34F63}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B254BC66-B276-415F-BFEC-DFBCB3E0CC89}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -65209,17 +65216,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3DA60A8-A10C-4376-830A-0871C6C34F63}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F5FD0BB-4DCC-421A-9E3C-B5ABA38AFD84}">
   <ds:schemaRefs>
